--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -3102,7 +3102,7 @@
         <v>137100827</v>
       </c>
       <c r="B25" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>137104225</v>
       </c>
       <c r="B26" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
         <v>137104181</v>
       </c>
       <c r="B27" t="n">
-        <v>92550</v>
+        <v>92556</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>137104273</v>
       </c>
       <c r="B28" t="n">
-        <v>92550</v>
+        <v>92556</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>137104280</v>
       </c>
       <c r="B29" t="n">
-        <v>92550</v>
+        <v>92556</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4060,7 +4060,7 @@
         <v>137101641</v>
       </c>
       <c r="B34" t="n">
-        <v>101545</v>
+        <v>101551</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>137103680</v>
       </c>
       <c r="B35" t="n">
-        <v>101545</v>
+        <v>101551</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4614,7 +4614,7 @@
         <v>137101206</v>
       </c>
       <c r="B39" t="n">
-        <v>97472</v>
+        <v>97478</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>137102220</v>
       </c>
       <c r="B40" t="n">
-        <v>97472</v>
+        <v>97478</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>137103497</v>
       </c>
       <c r="B41" t="n">
-        <v>97472</v>
+        <v>97478</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>137100838</v>
       </c>
       <c r="B48" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
         <v>137103126</v>
       </c>
       <c r="B49" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -25412,7 +25412,7 @@
         <v>137100796</v>
       </c>
       <c r="B230" t="n">
-        <v>111341</v>
+        <v>111347</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -34778,7 +34778,7 @@
         <v>137102690</v>
       </c>
       <c r="B313" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -34885,7 +34885,7 @@
         <v>137102722</v>
       </c>
       <c r="B314" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -34992,7 +34992,7 @@
         <v>137104260</v>
       </c>
       <c r="B315" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -3102,7 +3102,7 @@
         <v>137100827</v>
       </c>
       <c r="B25" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>137104225</v>
       </c>
       <c r="B26" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
         <v>137104181</v>
       </c>
       <c r="B27" t="n">
-        <v>92556</v>
+        <v>92560</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>137104273</v>
       </c>
       <c r="B28" t="n">
-        <v>92556</v>
+        <v>92560</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>137104280</v>
       </c>
       <c r="B29" t="n">
-        <v>92556</v>
+        <v>92560</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>137100901</v>
       </c>
       <c r="B30" t="n">
-        <v>83350</v>
+        <v>83354</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>137101215</v>
       </c>
       <c r="B31" t="n">
-        <v>83350</v>
+        <v>83354</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>137101334</v>
       </c>
       <c r="B32" t="n">
-        <v>83350</v>
+        <v>83354</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>137101518</v>
       </c>
       <c r="B33" t="n">
-        <v>83350</v>
+        <v>83354</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4060,7 +4060,7 @@
         <v>137101641</v>
       </c>
       <c r="B34" t="n">
-        <v>101551</v>
+        <v>101555</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>137103680</v>
       </c>
       <c r="B35" t="n">
-        <v>101551</v>
+        <v>101555</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4614,7 +4614,7 @@
         <v>137101206</v>
       </c>
       <c r="B39" t="n">
-        <v>97478</v>
+        <v>97482</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>137102220</v>
       </c>
       <c r="B40" t="n">
-        <v>97478</v>
+        <v>97482</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>137103497</v>
       </c>
       <c r="B41" t="n">
-        <v>97478</v>
+        <v>97482</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>137100838</v>
       </c>
       <c r="B48" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
         <v>137103126</v>
       </c>
       <c r="B49" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -7825,7 +7825,7 @@
         <v>137100759</v>
       </c>
       <c r="B69" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7927,7 +7927,7 @@
         <v>137100764</v>
       </c>
       <c r="B70" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         <v>137100823</v>
       </c>
       <c r="B71" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
         <v>137100857</v>
       </c>
       <c r="B72" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
         <v>137100888</v>
       </c>
       <c r="B73" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8355,7 +8355,7 @@
         <v>137100916</v>
       </c>
       <c r="B74" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8457,7 +8457,7 @@
         <v>137101034</v>
       </c>
       <c r="B75" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         <v>137101088</v>
       </c>
       <c r="B76" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8681,7 +8681,7 @@
         <v>137101127</v>
       </c>
       <c r="B77" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>137101148</v>
       </c>
       <c r="B78" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8895,7 +8895,7 @@
         <v>137101218</v>
       </c>
       <c r="B79" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9007,7 +9007,7 @@
         <v>137101220</v>
       </c>
       <c r="B80" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>137101234</v>
       </c>
       <c r="B81" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9216,7 +9216,7 @@
         <v>137101273</v>
       </c>
       <c r="B82" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>137101341</v>
       </c>
       <c r="B83" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9430,7 +9430,7 @@
         <v>137101461</v>
       </c>
       <c r="B84" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         <v>137101505</v>
       </c>
       <c r="B85" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9649,7 +9649,7 @@
         <v>137101722</v>
       </c>
       <c r="B86" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         <v>137101762</v>
       </c>
       <c r="B87" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9853,7 +9853,7 @@
         <v>137101804</v>
       </c>
       <c r="B88" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9955,7 +9955,7 @@
         <v>137101833</v>
       </c>
       <c r="B89" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10057,7 +10057,7 @@
         <v>137101847</v>
       </c>
       <c r="B90" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
         <v>137101896</v>
       </c>
       <c r="B91" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10266,7 +10266,7 @@
         <v>137101963</v>
       </c>
       <c r="B92" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10368,7 +10368,7 @@
         <v>137102051</v>
       </c>
       <c r="B93" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         <v>137102124</v>
       </c>
       <c r="B94" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10577,7 +10577,7 @@
         <v>137102177</v>
       </c>
       <c r="B95" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10679,7 +10679,7 @@
         <v>137102338</v>
       </c>
       <c r="B96" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         <v>137102389</v>
       </c>
       <c r="B97" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10883,7 +10883,7 @@
         <v>137102522</v>
       </c>
       <c r="B98" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10990,7 +10990,7 @@
         <v>137102735</v>
       </c>
       <c r="B99" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>137102892</v>
       </c>
       <c r="B100" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>137103082</v>
       </c>
       <c r="B101" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11301,7 +11301,7 @@
         <v>137103089</v>
       </c>
       <c r="B102" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11408,7 +11408,7 @@
         <v>137103465</v>
       </c>
       <c r="B103" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         <v>137103898</v>
       </c>
       <c r="B104" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11622,7 +11622,7 @@
         <v>137103902</v>
       </c>
       <c r="B105" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11724,7 +11724,7 @@
         <v>137104013</v>
       </c>
       <c r="B106" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11831,7 +11831,7 @@
         <v>137101366</v>
       </c>
       <c r="B107" t="n">
-        <v>79507</v>
+        <v>79509</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
         <v>137102792</v>
       </c>
       <c r="B110" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12260,7 +12260,7 @@
         <v>137103940</v>
       </c>
       <c r="B111" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -17724,7 +17724,7 @@
         <v>137101897</v>
       </c>
       <c r="B162" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17836,7 +17836,7 @@
         <v>137102434</v>
       </c>
       <c r="B163" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17938,7 +17938,7 @@
         <v>137102448</v>
       </c>
       <c r="B164" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18040,7 +18040,7 @@
         <v>137102599</v>
       </c>
       <c r="B165" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18142,7 +18142,7 @@
         <v>137102914</v>
       </c>
       <c r="B166" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18244,7 +18244,7 @@
         <v>137103290</v>
       </c>
       <c r="B167" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18346,7 +18346,7 @@
         <v>137103397</v>
       </c>
       <c r="B168" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18448,7 +18448,7 @@
         <v>137104161</v>
       </c>
       <c r="B169" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>137104195</v>
       </c>
       <c r="B170" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18662,7 +18662,7 @@
         <v>137101201</v>
       </c>
       <c r="B171" t="n">
-        <v>80602</v>
+        <v>80604</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19278,7 +19278,7 @@
         <v>137100972</v>
       </c>
       <c r="B177" t="n">
-        <v>80603</v>
+        <v>80605</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>137101009</v>
       </c>
       <c r="B178" t="n">
-        <v>80603</v>
+        <v>80605</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19492,7 +19492,7 @@
         <v>137101113</v>
       </c>
       <c r="B179" t="n">
-        <v>80603</v>
+        <v>80605</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>137101938</v>
       </c>
       <c r="B180" t="n">
-        <v>80603</v>
+        <v>80605</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19696,7 +19696,7 @@
         <v>137102630</v>
       </c>
       <c r="B181" t="n">
-        <v>80603</v>
+        <v>80605</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19798,7 +19798,7 @@
         <v>137103179</v>
       </c>
       <c r="B182" t="n">
-        <v>80603</v>
+        <v>80605</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -25412,7 +25412,7 @@
         <v>137100796</v>
       </c>
       <c r="B230" t="n">
-        <v>111347</v>
+        <v>111351</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -34778,7 +34778,7 @@
         <v>137102690</v>
       </c>
       <c r="B313" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -34885,7 +34885,7 @@
         <v>137102722</v>
       </c>
       <c r="B314" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -34992,7 +34992,7 @@
         <v>137104260</v>
       </c>
       <c r="B315" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -36428,7 +36428,7 @@
         <v>137101464</v>
       </c>
       <c r="B328" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -4060,7 +4060,7 @@
         <v>137101641</v>
       </c>
       <c r="B34" t="n">
-        <v>101555</v>
+        <v>101557</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>137103680</v>
       </c>
       <c r="B35" t="n">
-        <v>101555</v>
+        <v>101557</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4614,7 +4614,7 @@
         <v>137101206</v>
       </c>
       <c r="B39" t="n">
-        <v>97482</v>
+        <v>97484</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>137102220</v>
       </c>
       <c r="B40" t="n">
-        <v>97482</v>
+        <v>97484</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>137103497</v>
       </c>
       <c r="B41" t="n">
-        <v>97482</v>
+        <v>97484</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -25412,7 +25412,7 @@
         <v>137100796</v>
       </c>
       <c r="B230" t="n">
-        <v>111351</v>
+        <v>111353</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -34778,7 +34778,7 @@
         <v>137102690</v>
       </c>
       <c r="B313" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -34885,7 +34885,7 @@
         <v>137102722</v>
       </c>
       <c r="B314" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -34992,7 +34992,7 @@
         <v>137104260</v>
       </c>
       <c r="B315" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -3102,7 +3102,7 @@
         <v>137100827</v>
       </c>
       <c r="B25" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>137104225</v>
       </c>
       <c r="B26" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
         <v>137104181</v>
       </c>
       <c r="B27" t="n">
-        <v>92560</v>
+        <v>92562</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>137104273</v>
       </c>
       <c r="B28" t="n">
-        <v>92560</v>
+        <v>92562</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>137104280</v>
       </c>
       <c r="B29" t="n">
-        <v>92560</v>
+        <v>92562</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>137100901</v>
       </c>
       <c r="B30" t="n">
-        <v>83354</v>
+        <v>83356</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>137101215</v>
       </c>
       <c r="B31" t="n">
-        <v>83354</v>
+        <v>83356</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>137101334</v>
       </c>
       <c r="B32" t="n">
-        <v>83354</v>
+        <v>83356</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>137101518</v>
       </c>
       <c r="B33" t="n">
-        <v>83354</v>
+        <v>83356</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4060,7 +4060,7 @@
         <v>137101641</v>
       </c>
       <c r="B34" t="n">
-        <v>101557</v>
+        <v>101559</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>137103680</v>
       </c>
       <c r="B35" t="n">
-        <v>101557</v>
+        <v>101559</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4614,7 +4614,7 @@
         <v>137101206</v>
       </c>
       <c r="B39" t="n">
-        <v>97484</v>
+        <v>97486</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>137102220</v>
       </c>
       <c r="B40" t="n">
-        <v>97484</v>
+        <v>97486</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>137103497</v>
       </c>
       <c r="B41" t="n">
-        <v>97484</v>
+        <v>97486</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>137100838</v>
       </c>
       <c r="B48" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
         <v>137103126</v>
       </c>
       <c r="B49" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -7825,7 +7825,7 @@
         <v>137100759</v>
       </c>
       <c r="B69" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7927,7 +7927,7 @@
         <v>137100764</v>
       </c>
       <c r="B70" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         <v>137100823</v>
       </c>
       <c r="B71" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
         <v>137100857</v>
       </c>
       <c r="B72" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
         <v>137100888</v>
       </c>
       <c r="B73" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8355,7 +8355,7 @@
         <v>137100916</v>
       </c>
       <c r="B74" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8457,7 +8457,7 @@
         <v>137101034</v>
       </c>
       <c r="B75" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         <v>137101088</v>
       </c>
       <c r="B76" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8681,7 +8681,7 @@
         <v>137101127</v>
       </c>
       <c r="B77" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>137101148</v>
       </c>
       <c r="B78" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8895,7 +8895,7 @@
         <v>137101218</v>
       </c>
       <c r="B79" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9007,7 +9007,7 @@
         <v>137101220</v>
       </c>
       <c r="B80" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>137101234</v>
       </c>
       <c r="B81" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9216,7 +9216,7 @@
         <v>137101273</v>
       </c>
       <c r="B82" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>137101341</v>
       </c>
       <c r="B83" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9430,7 +9430,7 @@
         <v>137101461</v>
       </c>
       <c r="B84" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         <v>137101505</v>
       </c>
       <c r="B85" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9649,7 +9649,7 @@
         <v>137101722</v>
       </c>
       <c r="B86" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         <v>137101762</v>
       </c>
       <c r="B87" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9853,7 +9853,7 @@
         <v>137101804</v>
       </c>
       <c r="B88" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9955,7 +9955,7 @@
         <v>137101833</v>
       </c>
       <c r="B89" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10057,7 +10057,7 @@
         <v>137101847</v>
       </c>
       <c r="B90" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
         <v>137101896</v>
       </c>
       <c r="B91" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10266,7 +10266,7 @@
         <v>137101963</v>
       </c>
       <c r="B92" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10368,7 +10368,7 @@
         <v>137102051</v>
       </c>
       <c r="B93" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         <v>137102124</v>
       </c>
       <c r="B94" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10577,7 +10577,7 @@
         <v>137102177</v>
       </c>
       <c r="B95" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10679,7 +10679,7 @@
         <v>137102338</v>
       </c>
       <c r="B96" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         <v>137102389</v>
       </c>
       <c r="B97" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10883,7 +10883,7 @@
         <v>137102522</v>
       </c>
       <c r="B98" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10990,7 +10990,7 @@
         <v>137102735</v>
       </c>
       <c r="B99" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>137102892</v>
       </c>
       <c r="B100" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>137103082</v>
       </c>
       <c r="B101" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11301,7 +11301,7 @@
         <v>137103089</v>
       </c>
       <c r="B102" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11408,7 +11408,7 @@
         <v>137103465</v>
       </c>
       <c r="B103" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         <v>137103898</v>
       </c>
       <c r="B104" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11622,7 +11622,7 @@
         <v>137103902</v>
       </c>
       <c r="B105" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11724,7 +11724,7 @@
         <v>137104013</v>
       </c>
       <c r="B106" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11831,7 +11831,7 @@
         <v>137101366</v>
       </c>
       <c r="B107" t="n">
-        <v>79509</v>
+        <v>79512</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
         <v>137102792</v>
       </c>
       <c r="B110" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12260,7 +12260,7 @@
         <v>137103940</v>
       </c>
       <c r="B111" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -17724,7 +17724,7 @@
         <v>137101897</v>
       </c>
       <c r="B162" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17836,7 +17836,7 @@
         <v>137102434</v>
       </c>
       <c r="B163" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17938,7 +17938,7 @@
         <v>137102448</v>
       </c>
       <c r="B164" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18040,7 +18040,7 @@
         <v>137102599</v>
       </c>
       <c r="B165" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18142,7 +18142,7 @@
         <v>137102914</v>
       </c>
       <c r="B166" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18244,7 +18244,7 @@
         <v>137103290</v>
       </c>
       <c r="B167" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18346,7 +18346,7 @@
         <v>137103397</v>
       </c>
       <c r="B168" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18448,7 +18448,7 @@
         <v>137104161</v>
       </c>
       <c r="B169" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>137104195</v>
       </c>
       <c r="B170" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18662,7 +18662,7 @@
         <v>137101201</v>
       </c>
       <c r="B171" t="n">
-        <v>80604</v>
+        <v>80607</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19278,7 +19278,7 @@
         <v>137100972</v>
       </c>
       <c r="B177" t="n">
-        <v>80605</v>
+        <v>80608</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>137101009</v>
       </c>
       <c r="B178" t="n">
-        <v>80605</v>
+        <v>80608</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19492,7 +19492,7 @@
         <v>137101113</v>
       </c>
       <c r="B179" t="n">
-        <v>80605</v>
+        <v>80608</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>137101938</v>
       </c>
       <c r="B180" t="n">
-        <v>80605</v>
+        <v>80608</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19696,7 +19696,7 @@
         <v>137102630</v>
       </c>
       <c r="B181" t="n">
-        <v>80605</v>
+        <v>80608</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19798,7 +19798,7 @@
         <v>137103179</v>
       </c>
       <c r="B182" t="n">
-        <v>80605</v>
+        <v>80608</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -25412,7 +25412,7 @@
         <v>137100796</v>
       </c>
       <c r="B230" t="n">
-        <v>111353</v>
+        <v>111355</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -34778,7 +34778,7 @@
         <v>137102690</v>
       </c>
       <c r="B313" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -34885,7 +34885,7 @@
         <v>137102722</v>
       </c>
       <c r="B314" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -34992,7 +34992,7 @@
         <v>137104260</v>
       </c>
       <c r="B315" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -36428,7 +36428,7 @@
         <v>137101464</v>
       </c>
       <c r="B328" t="n">
-        <v>79508</v>
+        <v>79511</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -3102,7 +3102,7 @@
         <v>137100827</v>
       </c>
       <c r="B25" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>137104225</v>
       </c>
       <c r="B26" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
         <v>137104181</v>
       </c>
       <c r="B27" t="n">
-        <v>92562</v>
+        <v>92575</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>137104273</v>
       </c>
       <c r="B28" t="n">
-        <v>92562</v>
+        <v>92575</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>137104280</v>
       </c>
       <c r="B29" t="n">
-        <v>92562</v>
+        <v>92575</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>137100901</v>
       </c>
       <c r="B30" t="n">
-        <v>83356</v>
+        <v>83369</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>137101215</v>
       </c>
       <c r="B31" t="n">
-        <v>83356</v>
+        <v>83369</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>137101334</v>
       </c>
       <c r="B32" t="n">
-        <v>83356</v>
+        <v>83369</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>137101518</v>
       </c>
       <c r="B33" t="n">
-        <v>83356</v>
+        <v>83369</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4060,7 +4060,7 @@
         <v>137101641</v>
       </c>
       <c r="B34" t="n">
-        <v>101559</v>
+        <v>101572</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>137103680</v>
       </c>
       <c r="B35" t="n">
-        <v>101559</v>
+        <v>101572</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4614,7 +4614,7 @@
         <v>137101206</v>
       </c>
       <c r="B39" t="n">
-        <v>97486</v>
+        <v>97499</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>137102220</v>
       </c>
       <c r="B40" t="n">
-        <v>97486</v>
+        <v>97499</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>137103497</v>
       </c>
       <c r="B41" t="n">
-        <v>97486</v>
+        <v>97499</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>137100838</v>
       </c>
       <c r="B48" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
         <v>137103126</v>
       </c>
       <c r="B49" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -7825,7 +7825,7 @@
         <v>137100759</v>
       </c>
       <c r="B69" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7927,7 +7927,7 @@
         <v>137100764</v>
       </c>
       <c r="B70" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         <v>137100823</v>
       </c>
       <c r="B71" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
         <v>137100857</v>
       </c>
       <c r="B72" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
         <v>137100888</v>
       </c>
       <c r="B73" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8355,7 +8355,7 @@
         <v>137100916</v>
       </c>
       <c r="B74" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8457,7 +8457,7 @@
         <v>137101034</v>
       </c>
       <c r="B75" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         <v>137101088</v>
       </c>
       <c r="B76" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8681,7 +8681,7 @@
         <v>137101127</v>
       </c>
       <c r="B77" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>137101148</v>
       </c>
       <c r="B78" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8895,7 +8895,7 @@
         <v>137101218</v>
       </c>
       <c r="B79" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9007,7 +9007,7 @@
         <v>137101220</v>
       </c>
       <c r="B80" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>137101234</v>
       </c>
       <c r="B81" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9216,7 +9216,7 @@
         <v>137101273</v>
       </c>
       <c r="B82" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>137101341</v>
       </c>
       <c r="B83" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9430,7 +9430,7 @@
         <v>137101461</v>
       </c>
       <c r="B84" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         <v>137101505</v>
       </c>
       <c r="B85" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9649,7 +9649,7 @@
         <v>137101722</v>
       </c>
       <c r="B86" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         <v>137101762</v>
       </c>
       <c r="B87" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9853,7 +9853,7 @@
         <v>137101804</v>
       </c>
       <c r="B88" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9955,7 +9955,7 @@
         <v>137101833</v>
       </c>
       <c r="B89" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10057,7 +10057,7 @@
         <v>137101847</v>
       </c>
       <c r="B90" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
         <v>137101896</v>
       </c>
       <c r="B91" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10266,7 +10266,7 @@
         <v>137101963</v>
       </c>
       <c r="B92" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10368,7 +10368,7 @@
         <v>137102051</v>
       </c>
       <c r="B93" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         <v>137102124</v>
       </c>
       <c r="B94" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10577,7 +10577,7 @@
         <v>137102177</v>
       </c>
       <c r="B95" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10679,7 +10679,7 @@
         <v>137102338</v>
       </c>
       <c r="B96" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         <v>137102389</v>
       </c>
       <c r="B97" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10883,7 +10883,7 @@
         <v>137102522</v>
       </c>
       <c r="B98" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10990,7 +10990,7 @@
         <v>137102735</v>
       </c>
       <c r="B99" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>137102892</v>
       </c>
       <c r="B100" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>137103082</v>
       </c>
       <c r="B101" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11301,7 +11301,7 @@
         <v>137103089</v>
       </c>
       <c r="B102" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11408,7 +11408,7 @@
         <v>137103465</v>
       </c>
       <c r="B103" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         <v>137103898</v>
       </c>
       <c r="B104" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11622,7 +11622,7 @@
         <v>137103902</v>
       </c>
       <c r="B105" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11724,7 +11724,7 @@
         <v>137104013</v>
       </c>
       <c r="B106" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11831,7 +11831,7 @@
         <v>137101366</v>
       </c>
       <c r="B107" t="n">
-        <v>79512</v>
+        <v>79525</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
         <v>137102792</v>
       </c>
       <c r="B110" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12260,7 +12260,7 @@
         <v>137103940</v>
       </c>
       <c r="B111" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -17724,7 +17724,7 @@
         <v>137101897</v>
       </c>
       <c r="B162" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17836,7 +17836,7 @@
         <v>137102434</v>
       </c>
       <c r="B163" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17938,7 +17938,7 @@
         <v>137102448</v>
       </c>
       <c r="B164" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18040,7 +18040,7 @@
         <v>137102599</v>
       </c>
       <c r="B165" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18142,7 +18142,7 @@
         <v>137102914</v>
       </c>
       <c r="B166" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18244,7 +18244,7 @@
         <v>137103290</v>
       </c>
       <c r="B167" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18346,7 +18346,7 @@
         <v>137103397</v>
       </c>
       <c r="B168" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18448,7 +18448,7 @@
         <v>137104161</v>
       </c>
       <c r="B169" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>137104195</v>
       </c>
       <c r="B170" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18662,7 +18662,7 @@
         <v>137101201</v>
       </c>
       <c r="B171" t="n">
-        <v>80607</v>
+        <v>80620</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19278,7 +19278,7 @@
         <v>137100972</v>
       </c>
       <c r="B177" t="n">
-        <v>80608</v>
+        <v>80621</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>137101009</v>
       </c>
       <c r="B178" t="n">
-        <v>80608</v>
+        <v>80621</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19492,7 +19492,7 @@
         <v>137101113</v>
       </c>
       <c r="B179" t="n">
-        <v>80608</v>
+        <v>80621</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>137101938</v>
       </c>
       <c r="B180" t="n">
-        <v>80608</v>
+        <v>80621</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19696,7 +19696,7 @@
         <v>137102630</v>
       </c>
       <c r="B181" t="n">
-        <v>80608</v>
+        <v>80621</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19798,7 +19798,7 @@
         <v>137103179</v>
       </c>
       <c r="B182" t="n">
-        <v>80608</v>
+        <v>80621</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -24380,7 +24380,7 @@
         <v>137107193</v>
       </c>
       <c r="B221" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -24495,7 +24495,7 @@
         <v>137100836</v>
       </c>
       <c r="B222" t="n">
-        <v>57186</v>
+        <v>57199</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -24844,7 +24844,7 @@
         <v>137100951</v>
       </c>
       <c r="B225" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -24965,7 +24965,7 @@
         <v>137101421</v>
       </c>
       <c r="B226" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -25076,7 +25076,7 @@
         <v>137102402</v>
       </c>
       <c r="B227" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -25412,7 +25412,7 @@
         <v>137100796</v>
       </c>
       <c r="B230" t="n">
-        <v>111355</v>
+        <v>111368</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -34778,7 +34778,7 @@
         <v>137102690</v>
       </c>
       <c r="B313" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -34885,7 +34885,7 @@
         <v>137102722</v>
       </c>
       <c r="B314" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -34992,7 +34992,7 @@
         <v>137104260</v>
       </c>
       <c r="B315" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -36428,7 +36428,7 @@
         <v>137101464</v>
       </c>
       <c r="B328" t="n">
-        <v>79511</v>
+        <v>79524</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -3102,7 +3102,7 @@
         <v>137100827</v>
       </c>
       <c r="B25" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>137104225</v>
       </c>
       <c r="B26" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
         <v>137104181</v>
       </c>
       <c r="B27" t="n">
-        <v>92575</v>
+        <v>92577</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>137104273</v>
       </c>
       <c r="B28" t="n">
-        <v>92575</v>
+        <v>92577</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>137104280</v>
       </c>
       <c r="B29" t="n">
-        <v>92575</v>
+        <v>92577</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>137100901</v>
       </c>
       <c r="B30" t="n">
-        <v>83369</v>
+        <v>83371</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>137101215</v>
       </c>
       <c r="B31" t="n">
-        <v>83369</v>
+        <v>83371</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>137101334</v>
       </c>
       <c r="B32" t="n">
-        <v>83369</v>
+        <v>83371</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>137101518</v>
       </c>
       <c r="B33" t="n">
-        <v>83369</v>
+        <v>83371</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4060,7 +4060,7 @@
         <v>137101641</v>
       </c>
       <c r="B34" t="n">
-        <v>101572</v>
+        <v>101574</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>137103680</v>
       </c>
       <c r="B35" t="n">
-        <v>101572</v>
+        <v>101574</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4614,7 +4614,7 @@
         <v>137101206</v>
       </c>
       <c r="B39" t="n">
-        <v>97499</v>
+        <v>97501</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>137102220</v>
       </c>
       <c r="B40" t="n">
-        <v>97499</v>
+        <v>97501</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>137103497</v>
       </c>
       <c r="B41" t="n">
-        <v>97499</v>
+        <v>97501</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>137100838</v>
       </c>
       <c r="B48" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
         <v>137103126</v>
       </c>
       <c r="B49" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -7825,7 +7825,7 @@
         <v>137100759</v>
       </c>
       <c r="B69" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7927,7 +7927,7 @@
         <v>137100764</v>
       </c>
       <c r="B70" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         <v>137100823</v>
       </c>
       <c r="B71" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
         <v>137100857</v>
       </c>
       <c r="B72" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
         <v>137100888</v>
       </c>
       <c r="B73" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8355,7 +8355,7 @@
         <v>137100916</v>
       </c>
       <c r="B74" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8457,7 +8457,7 @@
         <v>137101034</v>
       </c>
       <c r="B75" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         <v>137101088</v>
       </c>
       <c r="B76" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8681,7 +8681,7 @@
         <v>137101127</v>
       </c>
       <c r="B77" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>137101148</v>
       </c>
       <c r="B78" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8895,7 +8895,7 @@
         <v>137101218</v>
       </c>
       <c r="B79" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9007,7 +9007,7 @@
         <v>137101220</v>
       </c>
       <c r="B80" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>137101234</v>
       </c>
       <c r="B81" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9216,7 +9216,7 @@
         <v>137101273</v>
       </c>
       <c r="B82" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>137101341</v>
       </c>
       <c r="B83" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9430,7 +9430,7 @@
         <v>137101461</v>
       </c>
       <c r="B84" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         <v>137101505</v>
       </c>
       <c r="B85" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9649,7 +9649,7 @@
         <v>137101722</v>
       </c>
       <c r="B86" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         <v>137101762</v>
       </c>
       <c r="B87" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9853,7 +9853,7 @@
         <v>137101804</v>
       </c>
       <c r="B88" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9955,7 +9955,7 @@
         <v>137101833</v>
       </c>
       <c r="B89" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10057,7 +10057,7 @@
         <v>137101847</v>
       </c>
       <c r="B90" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
         <v>137101896</v>
       </c>
       <c r="B91" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10266,7 +10266,7 @@
         <v>137101963</v>
       </c>
       <c r="B92" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10368,7 +10368,7 @@
         <v>137102051</v>
       </c>
       <c r="B93" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         <v>137102124</v>
       </c>
       <c r="B94" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10577,7 +10577,7 @@
         <v>137102177</v>
       </c>
       <c r="B95" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10679,7 +10679,7 @@
         <v>137102338</v>
       </c>
       <c r="B96" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         <v>137102389</v>
       </c>
       <c r="B97" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10883,7 +10883,7 @@
         <v>137102522</v>
       </c>
       <c r="B98" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10990,7 +10990,7 @@
         <v>137102735</v>
       </c>
       <c r="B99" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>137102892</v>
       </c>
       <c r="B100" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>137103082</v>
       </c>
       <c r="B101" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11301,7 +11301,7 @@
         <v>137103089</v>
       </c>
       <c r="B102" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11408,7 +11408,7 @@
         <v>137103465</v>
       </c>
       <c r="B103" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         <v>137103898</v>
       </c>
       <c r="B104" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11622,7 +11622,7 @@
         <v>137103902</v>
       </c>
       <c r="B105" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11724,7 +11724,7 @@
         <v>137104013</v>
       </c>
       <c r="B106" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11831,7 +11831,7 @@
         <v>137101366</v>
       </c>
       <c r="B107" t="n">
-        <v>79525</v>
+        <v>79527</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
         <v>137102792</v>
       </c>
       <c r="B110" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12260,7 +12260,7 @@
         <v>137103940</v>
       </c>
       <c r="B111" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -17724,7 +17724,7 @@
         <v>137101897</v>
       </c>
       <c r="B162" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17836,7 +17836,7 @@
         <v>137102434</v>
       </c>
       <c r="B163" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17938,7 +17938,7 @@
         <v>137102448</v>
       </c>
       <c r="B164" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18040,7 +18040,7 @@
         <v>137102599</v>
       </c>
       <c r="B165" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18142,7 +18142,7 @@
         <v>137102914</v>
       </c>
       <c r="B166" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18244,7 +18244,7 @@
         <v>137103290</v>
       </c>
       <c r="B167" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18346,7 +18346,7 @@
         <v>137103397</v>
       </c>
       <c r="B168" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18448,7 +18448,7 @@
         <v>137104161</v>
       </c>
       <c r="B169" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>137104195</v>
       </c>
       <c r="B170" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18662,7 +18662,7 @@
         <v>137101201</v>
       </c>
       <c r="B171" t="n">
-        <v>80620</v>
+        <v>80622</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19278,7 +19278,7 @@
         <v>137100972</v>
       </c>
       <c r="B177" t="n">
-        <v>80621</v>
+        <v>80623</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>137101009</v>
       </c>
       <c r="B178" t="n">
-        <v>80621</v>
+        <v>80623</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19492,7 +19492,7 @@
         <v>137101113</v>
       </c>
       <c r="B179" t="n">
-        <v>80621</v>
+        <v>80623</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>137101938</v>
       </c>
       <c r="B180" t="n">
-        <v>80621</v>
+        <v>80623</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19696,7 +19696,7 @@
         <v>137102630</v>
       </c>
       <c r="B181" t="n">
-        <v>80621</v>
+        <v>80623</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19798,7 +19798,7 @@
         <v>137103179</v>
       </c>
       <c r="B182" t="n">
-        <v>80621</v>
+        <v>80623</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -24380,7 +24380,7 @@
         <v>137107193</v>
       </c>
       <c r="B221" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -24495,7 +24495,7 @@
         <v>137100836</v>
       </c>
       <c r="B222" t="n">
-        <v>57199</v>
+        <v>57201</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -24844,7 +24844,7 @@
         <v>137100951</v>
       </c>
       <c r="B225" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -24965,7 +24965,7 @@
         <v>137101421</v>
       </c>
       <c r="B226" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -25076,7 +25076,7 @@
         <v>137102402</v>
       </c>
       <c r="B227" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -25412,7 +25412,7 @@
         <v>137100796</v>
       </c>
       <c r="B230" t="n">
-        <v>111368</v>
+        <v>111370</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -34778,7 +34778,7 @@
         <v>137102690</v>
       </c>
       <c r="B313" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -34885,7 +34885,7 @@
         <v>137102722</v>
       </c>
       <c r="B314" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -34992,7 +34992,7 @@
         <v>137104260</v>
       </c>
       <c r="B315" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -36428,7 +36428,7 @@
         <v>137101464</v>
       </c>
       <c r="B328" t="n">
-        <v>79524</v>
+        <v>79526</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -24408,11 +24408,7 @@
       <c r="I221" t="inlineStr"/>
       <c r="K221" t="inlineStr"/>
       <c r="L221" t="inlineStr"/>
-      <c r="M221" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
+      <c r="M221" t="inlineStr"/>
       <c r="N221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
@@ -24525,11 +24521,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M222" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
           <t>Kyrkviken, Kläppsjö, Ång</t>
@@ -24874,11 +24866,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M225" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="M225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
           <t>Kyrkviken, Kläppsjö, Ång</t>
@@ -25102,11 +25090,7 @@
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
-      <c r="M227" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
           <t>Kyrkviken, Ång</t>

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -3102,7 +3102,7 @@
         <v>137100827</v>
       </c>
       <c r="B25" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>137104225</v>
       </c>
       <c r="B26" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
         <v>137104181</v>
       </c>
       <c r="B27" t="n">
-        <v>92577</v>
+        <v>92580</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>137104273</v>
       </c>
       <c r="B28" t="n">
-        <v>92577</v>
+        <v>92580</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>137104280</v>
       </c>
       <c r="B29" t="n">
-        <v>92577</v>
+        <v>92580</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4060,7 +4060,7 @@
         <v>137101641</v>
       </c>
       <c r="B34" t="n">
-        <v>101574</v>
+        <v>101577</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>137103680</v>
       </c>
       <c r="B35" t="n">
-        <v>101574</v>
+        <v>101577</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4614,7 +4614,7 @@
         <v>137101206</v>
       </c>
       <c r="B39" t="n">
-        <v>97501</v>
+        <v>97504</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>137102220</v>
       </c>
       <c r="B40" t="n">
-        <v>97501</v>
+        <v>97504</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>137103497</v>
       </c>
       <c r="B41" t="n">
-        <v>97501</v>
+        <v>97504</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>137100838</v>
       </c>
       <c r="B48" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
         <v>137103126</v>
       </c>
       <c r="B49" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -25396,7 +25396,7 @@
         <v>137100796</v>
       </c>
       <c r="B230" t="n">
-        <v>111370</v>
+        <v>111376</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -34762,7 +34762,7 @@
         <v>137102690</v>
       </c>
       <c r="B313" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -34869,7 +34869,7 @@
         <v>137102722</v>
       </c>
       <c r="B314" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -34976,7 +34976,7 @@
         <v>137104260</v>
       </c>
       <c r="B315" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -3102,7 +3102,7 @@
         <v>137100827</v>
       </c>
       <c r="B25" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>137104225</v>
       </c>
       <c r="B26" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
         <v>137104181</v>
       </c>
       <c r="B27" t="n">
-        <v>92580</v>
+        <v>92590</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>137104273</v>
       </c>
       <c r="B28" t="n">
-        <v>92580</v>
+        <v>92590</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>137104280</v>
       </c>
       <c r="B29" t="n">
-        <v>92580</v>
+        <v>92590</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>137100901</v>
       </c>
       <c r="B30" t="n">
-        <v>83371</v>
+        <v>83381</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>137101215</v>
       </c>
       <c r="B31" t="n">
-        <v>83371</v>
+        <v>83381</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>137101334</v>
       </c>
       <c r="B32" t="n">
-        <v>83371</v>
+        <v>83381</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>137101518</v>
       </c>
       <c r="B33" t="n">
-        <v>83371</v>
+        <v>83381</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4060,7 +4060,7 @@
         <v>137101641</v>
       </c>
       <c r="B34" t="n">
-        <v>101577</v>
+        <v>101592</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>137103680</v>
       </c>
       <c r="B35" t="n">
-        <v>101577</v>
+        <v>101592</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4614,7 +4614,7 @@
         <v>137101206</v>
       </c>
       <c r="B39" t="n">
-        <v>97504</v>
+        <v>97514</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>137102220</v>
       </c>
       <c r="B40" t="n">
-        <v>97504</v>
+        <v>97514</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>137103497</v>
       </c>
       <c r="B41" t="n">
-        <v>97504</v>
+        <v>97514</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>137100838</v>
       </c>
       <c r="B48" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
         <v>137103126</v>
       </c>
       <c r="B49" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -7825,7 +7825,7 @@
         <v>137100759</v>
       </c>
       <c r="B69" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7927,7 +7927,7 @@
         <v>137100764</v>
       </c>
       <c r="B70" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         <v>137100823</v>
       </c>
       <c r="B71" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
         <v>137100857</v>
       </c>
       <c r="B72" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
         <v>137100888</v>
       </c>
       <c r="B73" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8355,7 +8355,7 @@
         <v>137100916</v>
       </c>
       <c r="B74" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8457,7 +8457,7 @@
         <v>137101034</v>
       </c>
       <c r="B75" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         <v>137101088</v>
       </c>
       <c r="B76" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8681,7 +8681,7 @@
         <v>137101127</v>
       </c>
       <c r="B77" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>137101148</v>
       </c>
       <c r="B78" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8895,7 +8895,7 @@
         <v>137101218</v>
       </c>
       <c r="B79" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9007,7 +9007,7 @@
         <v>137101220</v>
       </c>
       <c r="B80" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>137101234</v>
       </c>
       <c r="B81" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9216,7 +9216,7 @@
         <v>137101273</v>
       </c>
       <c r="B82" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>137101341</v>
       </c>
       <c r="B83" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9430,7 +9430,7 @@
         <v>137101461</v>
       </c>
       <c r="B84" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         <v>137101505</v>
       </c>
       <c r="B85" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9649,7 +9649,7 @@
         <v>137101722</v>
       </c>
       <c r="B86" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         <v>137101762</v>
       </c>
       <c r="B87" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9853,7 +9853,7 @@
         <v>137101804</v>
       </c>
       <c r="B88" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9955,7 +9955,7 @@
         <v>137101833</v>
       </c>
       <c r="B89" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10057,7 +10057,7 @@
         <v>137101847</v>
       </c>
       <c r="B90" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
         <v>137101896</v>
       </c>
       <c r="B91" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10266,7 +10266,7 @@
         <v>137101963</v>
       </c>
       <c r="B92" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10368,7 +10368,7 @@
         <v>137102051</v>
       </c>
       <c r="B93" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         <v>137102124</v>
       </c>
       <c r="B94" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10577,7 +10577,7 @@
         <v>137102177</v>
       </c>
       <c r="B95" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10679,7 +10679,7 @@
         <v>137102338</v>
       </c>
       <c r="B96" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         <v>137102389</v>
       </c>
       <c r="B97" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10883,7 +10883,7 @@
         <v>137102522</v>
       </c>
       <c r="B98" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10990,7 +10990,7 @@
         <v>137102735</v>
       </c>
       <c r="B99" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>137102892</v>
       </c>
       <c r="B100" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>137103082</v>
       </c>
       <c r="B101" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11301,7 +11301,7 @@
         <v>137103089</v>
       </c>
       <c r="B102" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11408,7 +11408,7 @@
         <v>137103465</v>
       </c>
       <c r="B103" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         <v>137103898</v>
       </c>
       <c r="B104" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11622,7 +11622,7 @@
         <v>137103902</v>
       </c>
       <c r="B105" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11724,7 +11724,7 @@
         <v>137104013</v>
       </c>
       <c r="B106" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11831,7 +11831,7 @@
         <v>137101366</v>
       </c>
       <c r="B107" t="n">
-        <v>79527</v>
+        <v>79537</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
         <v>137102792</v>
       </c>
       <c r="B110" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12260,7 +12260,7 @@
         <v>137103940</v>
       </c>
       <c r="B111" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -17724,7 +17724,7 @@
         <v>137101897</v>
       </c>
       <c r="B162" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17836,7 +17836,7 @@
         <v>137102434</v>
       </c>
       <c r="B163" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17938,7 +17938,7 @@
         <v>137102448</v>
       </c>
       <c r="B164" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18040,7 +18040,7 @@
         <v>137102599</v>
       </c>
       <c r="B165" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18142,7 +18142,7 @@
         <v>137102914</v>
       </c>
       <c r="B166" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18244,7 +18244,7 @@
         <v>137103290</v>
       </c>
       <c r="B167" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18346,7 +18346,7 @@
         <v>137103397</v>
       </c>
       <c r="B168" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18448,7 +18448,7 @@
         <v>137104161</v>
       </c>
       <c r="B169" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>137104195</v>
       </c>
       <c r="B170" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18662,7 +18662,7 @@
         <v>137101201</v>
       </c>
       <c r="B171" t="n">
-        <v>80622</v>
+        <v>80632</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19278,7 +19278,7 @@
         <v>137100972</v>
       </c>
       <c r="B177" t="n">
-        <v>80623</v>
+        <v>80633</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>137101009</v>
       </c>
       <c r="B178" t="n">
-        <v>80623</v>
+        <v>80633</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19492,7 +19492,7 @@
         <v>137101113</v>
       </c>
       <c r="B179" t="n">
-        <v>80623</v>
+        <v>80633</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>137101938</v>
       </c>
       <c r="B180" t="n">
-        <v>80623</v>
+        <v>80633</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19696,7 +19696,7 @@
         <v>137102630</v>
       </c>
       <c r="B181" t="n">
-        <v>80623</v>
+        <v>80633</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19798,7 +19798,7 @@
         <v>137103179</v>
       </c>
       <c r="B182" t="n">
-        <v>80623</v>
+        <v>80633</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -24380,7 +24380,7 @@
         <v>137107193</v>
       </c>
       <c r="B221" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -24491,7 +24491,7 @@
         <v>137100836</v>
       </c>
       <c r="B222" t="n">
-        <v>57201</v>
+        <v>57211</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -24836,7 +24836,7 @@
         <v>137100951</v>
       </c>
       <c r="B225" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -24953,7 +24953,7 @@
         <v>137101421</v>
       </c>
       <c r="B226" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -25064,7 +25064,7 @@
         <v>137102402</v>
       </c>
       <c r="B227" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -25396,7 +25396,7 @@
         <v>137100796</v>
       </c>
       <c r="B230" t="n">
-        <v>111376</v>
+        <v>111398</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -34762,7 +34762,7 @@
         <v>137102690</v>
       </c>
       <c r="B313" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -34869,7 +34869,7 @@
         <v>137102722</v>
       </c>
       <c r="B314" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -34976,7 +34976,7 @@
         <v>137104260</v>
       </c>
       <c r="B315" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -36412,7 +36412,7 @@
         <v>137101464</v>
       </c>
       <c r="B328" t="n">
-        <v>79526</v>
+        <v>79536</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -3102,7 +3102,7 @@
         <v>137100827</v>
       </c>
       <c r="B25" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>137104225</v>
       </c>
       <c r="B26" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
         <v>137104181</v>
       </c>
       <c r="B27" t="n">
-        <v>92590</v>
+        <v>92591</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>137104273</v>
       </c>
       <c r="B28" t="n">
-        <v>92590</v>
+        <v>92591</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>137104280</v>
       </c>
       <c r="B29" t="n">
-        <v>92590</v>
+        <v>92591</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4060,7 +4060,7 @@
         <v>137101641</v>
       </c>
       <c r="B34" t="n">
-        <v>101592</v>
+        <v>101593</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>137103680</v>
       </c>
       <c r="B35" t="n">
-        <v>101592</v>
+        <v>101593</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4614,7 +4614,7 @@
         <v>137101206</v>
       </c>
       <c r="B39" t="n">
-        <v>97514</v>
+        <v>97515</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>137102220</v>
       </c>
       <c r="B40" t="n">
-        <v>97514</v>
+        <v>97515</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>137103497</v>
       </c>
       <c r="B41" t="n">
-        <v>97514</v>
+        <v>97515</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>137100838</v>
       </c>
       <c r="B48" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
         <v>137103126</v>
       </c>
       <c r="B49" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -25396,7 +25396,7 @@
         <v>137100796</v>
       </c>
       <c r="B230" t="n">
-        <v>111398</v>
+        <v>111399</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -34762,7 +34762,7 @@
         <v>137102690</v>
       </c>
       <c r="B313" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -34869,7 +34869,7 @@
         <v>137102722</v>
       </c>
       <c r="B314" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -34976,7 +34976,7 @@
         <v>137104260</v>
       </c>
       <c r="B315" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
